--- a/course-design-2/outputs/tables/ch4/58_stage26_6_region_scope_audit.xlsx
+++ b/course-design-2/outputs/tables/ch4/58_stage26_6_region_scope_audit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_两个分析范围" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_代表城市两种统计范围对照" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_两个分析范围" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_代表城市两种统计范围对照" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,10 +492,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>data/processed/job_analysis_dataset.parquet（17,144 行）+ outputs/tables/ch4/55_stage26_5_province_distribution.xlsx</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>data/processed/job_analysis_dataset.parquet（17,144 行）+ outputs/tables/66_stage26_5_province_distribution.xlsx</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>上海市 5,293、北京市 5,265、广东省 2,322、江苏省 881、浙江省 853、四川省 700</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -509,11 +513,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14883</v>
+        <v>14380</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>按城市原值统计，不聚合到省级行政区；04_城市薪资列出 26 个城市取值（合计 14380 个岗位），其余取值未单列</t>
+          <t>按城市原值统计，不聚合到省级行政区</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -523,7 +527,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>outputs/tables/ch4/21_eda_statistical_analysis.xlsx / 04_城市薪资</t>
+          <t>outputs/tables/29_eda_statistical_analysis.xlsx / 04_城市薪资</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -582,7 +586,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>直辖市的城市值即省级行政区值，但两个统计范围的分母不同（17,144 与 14,883）</t>
+          <t>直辖市的城市值即省级行政区值，但两个口径的分母不同（17,144 与 14,883）</t>
         </is>
       </c>
     </row>
@@ -600,7 +604,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>同上；图中标签使用省域聚合范围</t>
+          <t>同上；图中标签使用省域聚合口径</t>
         </is>
       </c>
     </row>
@@ -618,7 +622,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>实体归属范围的深圳（1129 个）在省域地图中并入广东省</t>
+          <t>实体口径的深圳（1129 个）在省域地图中并入广东省</t>
         </is>
       </c>
     </row>
@@ -636,7 +640,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>实体归属范围的杭州（745 个）在省域地图中并入浙江省</t>
+          <t>实体口径的杭州（745 个）在省域地图中并入浙江省</t>
         </is>
       </c>
     </row>
